--- a/data/stats/supp_tables/yield-cc-pairwise.xlsx
+++ b/data/stats/supp_tables/yield-cc-pairwise.xlsx
@@ -11,6 +11,59 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>contrast</t>
+  </si>
+  <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>t.ratio</t>
+  </si>
+  <si>
+    <t>p.value</t>
+  </si>
+  <si>
+    <t>mix_E - mix_M</t>
+  </si>
+  <si>
+    <t>mix_E - nocc</t>
+  </si>
+  <si>
+    <t>mix_E - rad_L</t>
+  </si>
+  <si>
+    <t>mix_E - rad_M</t>
+  </si>
+  <si>
+    <t>mix_M - nocc</t>
+  </si>
+  <si>
+    <t>mix_M - rad_L</t>
+  </si>
+  <si>
+    <t>mix_M - rad_M</t>
+  </si>
+  <si>
+    <t>nocc - rad_L</t>
+  </si>
+  <si>
+    <t>nocc - rad_M</t>
+  </si>
+  <si>
+    <t>rad_L - rad_M</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,43 +407,29 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>contrast</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>t.ratio</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mix_E - mix_M</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0.03768333835396386</v>
@@ -408,11 +447,9 @@
         <v>0.9941570491371939</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mix_E - nocc</t>
-        </is>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>-0.007175311684324984</v>
@@ -430,11 +467,9 @@
         <v>0.9999916989476905</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mix_E - rad_L</t>
-        </is>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0.03185676212831729</v>
@@ -452,11 +487,9 @@
         <v>0.996946643873235</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mix_E - rad_M</t>
-        </is>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
       </c>
       <c r="B5">
         <v>-0.2845472703295057</v>
@@ -474,11 +507,9 @@
         <v>0.02462242930583347</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mix_M - nocc</t>
-        </is>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
       </c>
       <c r="B6">
         <v>-0.04485865003828884</v>
@@ -496,11 +527,9 @@
         <v>0.9886505870938722</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mix_M - rad_L</t>
-        </is>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
       </c>
       <c r="B7">
         <v>-0.005826576225646562</v>
@@ -518,11 +547,9 @@
         <v>0.9999963870720809</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>mix_M - rad_M</t>
-        </is>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
       </c>
       <c r="B8">
         <v>-0.3222306086834695</v>
@@ -540,11 +567,9 @@
         <v>0.007577751804564103</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>nocc - rad_L</t>
-        </is>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0.03903207381264227</v>
@@ -562,11 +587,9 @@
         <v>0.9933136230474391</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>nocc - rad_M</t>
-        </is>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
       </c>
       <c r="B10">
         <v>-0.2773719586451807</v>
@@ -584,11 +607,9 @@
         <v>0.03038163052141329</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>rad_L - rad_M</t>
-        </is>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
       </c>
       <c r="B11">
         <v>-0.3164040324578229</v>
